--- a/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-imaging-study.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="170">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t>Modalités d'imagerie utilisées lors de l'examen (DICOM CID029)</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-modalite-acquisition-cisis : Modalité d'imagerie</t>
@@ -2851,13 +2854,13 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2892,10 +2895,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2918,13 +2921,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2975,7 +2978,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -2992,10 +2995,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3018,13 +3021,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3075,7 +3078,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3092,10 +3095,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3121,10 +3124,10 @@
         <v>128</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3175,7 +3178,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3192,10 +3195,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3218,13 +3221,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3275,7 +3278,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3292,10 +3295,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3318,13 +3321,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3375,7 +3378,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3392,10 +3395,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3418,13 +3421,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3475,7 +3478,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3492,10 +3495,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3521,10 +3524,10 @@
         <v>100</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3575,7 +3578,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3592,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3618,13 +3621,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3675,7 +3678,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3692,10 +3695,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3718,13 +3721,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3775,7 +3778,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
